--- a/output/Data and Chart Outputs/sweden_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/sweden_power_capacity.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -155,7 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Sweden installed generating capacity (ENTSO-E, annual) (to Jan/26)</a:t>
+              <a:t>Sweden installed generating capacity (ENTSO-E, annual) (to 2026)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -185,12 +185,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2</f>
+              <f>'Chart'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -213,12 +213,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2</f>
+              <f>'Chart'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -241,12 +241,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2</f>
+              <f>'Chart'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -269,12 +269,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2</f>
+              <f>'Chart'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -297,12 +297,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2</f>
+              <f>'Chart'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -325,12 +325,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2</f>
+              <f>'Chart'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -353,12 +353,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2</f>
+              <f>'Chart'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -381,12 +381,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2</f>
+              <f>'Chart'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -402,7 +402,7 @@
         </scaling>
         <delete val="0"/>
         <axPos val="b"/>
-        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
+        <numFmt formatCode="yyyy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -873,7 +873,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-03 07:33 UTC; years 2026-2026</t>
+          <t>2026-10-03 10:55 UTC; years 2021-2026</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -943,30 +943,175 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B2" t="n">
+        <v>16.334</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10.017</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>14.848</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B4" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B5" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B6" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
         <v>46023</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B7" t="n">
         <v>16.416</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
         <v>14.274</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>13.338</v>
       </c>
     </row>
@@ -982,7 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,42 +1199,247 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B2" t="n">
+        <v>16334</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10017</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6871</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7977</v>
+      </c>
+      <c r="K2" t="n">
+        <v>41199</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B3" t="n">
+        <v>16300</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6900</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="K3" t="n">
+        <v>43700</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B4" t="n">
+        <v>16300</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14700</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6900</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>46900</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B5" t="n">
+        <v>16300</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16700</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6900</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6600</v>
+      </c>
+      <c r="K5" t="n">
+        <v>49700</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B6" t="n">
+        <v>16400</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6900</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6700</v>
+      </c>
+      <c r="K6" t="n">
+        <v>53000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
         <v>46023</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B7" t="n">
         <v>16416</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
         <v>14274</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>6800</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>6538</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K7" t="n">
         <v>44028</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/sweden_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/sweden_power_capacity.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Sweden installed generating capacity (ENTSO-E, annual) (to 2026)</a:t>
             </a:r>
           </a:p>
@@ -288,7 +289,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -316,7 +317,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -344,7 +345,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -372,7 +373,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -873,7 +874,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-03 10:55 UTC; years 2021-2026</t>
+          <t>2026-10-28 01:09 UTC; years 2021-2026</t>
         </is>
       </c>
     </row>
